--- a/דוח נכסים לתאריך:29-07-2026.xlsx
+++ b/דוח נכסים לתאריך:29-07-2026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,14 +29,20 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="10"/>
+      <color rgb="000563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -46,16 +52,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,16 +72,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="001F4E79"/>
+        <color rgb="00CCCCCC"/>
       </left>
       <right style="thin">
-        <color rgb="001F4E79"/>
+        <color rgb="00CCCCCC"/>
       </right>
       <top style="thin">
-        <color rgb="001F4E79"/>
+        <color rgb="00CCCCCC"/>
       </top>
       <bottom style="thin">
-        <color rgb="001F4E79"/>
+        <color rgb="00CCCCCC"/>
       </bottom>
     </border>
   </borders>
@@ -88,13 +91,13 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -461,19 +464,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>שם העסק</t>
@@ -510,20 +513,20 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ד"ר גרוס מנחם</t>
+          <t>קרן פנינה - בגדי גברים</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>הקבלן 27, ירושלים, הר נוף</t>
+          <t>הרב בצלאל זולטי 19, ירושלים</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>רופא ילדים</t>
+          <t>בגדי גברים</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -531,216 +534,13 @@
           <t>גבוה</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/16085530/46200/</t>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.b144.co.il/b144_sip/401C04134171675849140116/</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>עפרה הר כסף גולדשטיין</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>הקבלן 28, ירושלים</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>גרפולוגיה</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.b144.co.il/b144_sip/4A1404134470655D491601154578645F4E/</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>בית העדשות</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>הקבלן 39, ירושלים</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>עדשות מגע</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/80173884/37560/</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>אגם ברכונים ומזכרות</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>הקבלן 47, ירושלים</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>תשמישי קדושה ויודאיקה</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/23517160/52170/</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>אבני החושן</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>הקבלן 49, ירושלים</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>אבני חן</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/34966010/150/</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>בוסו הרב שלמה</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>הקבלן 49, ירושלים</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>מוהלים</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/80074377/23910/</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>שושי זה יופי (גולדברג)</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>הקבלן 61, ירושלים</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>פאות, תוספות והשתלת שיער</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/23868780/39330/</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>יד שרה</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>הקליר 6, ירושלים, שערי חסד</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>אגודות ארגונים ועמותות</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/39131420/300/</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
